--- a/Datas/Bullet.xlsx
+++ b/Datas/Bullet.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -118,10 +118,13 @@
     <t>NORMAL</t>
   </si>
   <si>
-    <t>normalbullet</t>
+    <t>garosbullet</t>
   </si>
   <si>
     <t>MONSTER</t>
+  </si>
+  <si>
+    <t>alicebullet</t>
   </si>
   <si>
     <t>HERO</t>
@@ -1271,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
